--- a/out/LSTM-Mamba1_repeat_3_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8554444171274074</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.228705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.228705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.228705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000391969883532729</v>
+        <v>-6.75351114863297e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.518833854729427</v>
+        <v>0.7785800168151985</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
-        <v>9.044653011089986</v>
+        <v>1.558363729382479</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6776192940205544</v>
+        <v>0.1167515465921939</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.874992847803057</v>
+        <v>1.012241738182021</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.8472445438445323</v>
+        <v>0.1459774784774187</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.891970365717502</v>
+        <v>1.18746364413097</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.214521198302129</v>
+        <v>0.209257860438623</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>8.474246242655786</v>
+        <v>1.460084593687064</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.299297110085373</v>
+        <v>0.2238644609173098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.85840981704181</v>
+        <v>1.698571628299907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.376992313482098</v>
+        <v>0.237251944347076</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.228705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>11.31319712833096</v>
+        <v>1.949227299831098</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.6214110207047058</v>
+        <v>0.1070667240257002</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>11.17788243713265</v>
+        <v>1.925912980847788</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.3001137636143597</v>
+        <v>0.05170897721724928</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>11.15621033973502</v>
+        <v>1.922178923545358</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.142994660511181</v>
+        <v>0.02463717527422079</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>11.14184879192911</v>
+        <v>1.919704459501471</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.04236868364818479</v>
+        <v>0.007297419349351257</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>11.08343795528665</v>
+        <v>1.909637419604475</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02802530428311959</v>
+        <v>0.004825271689484421</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>11.09709775777395</v>
+        <v>1.911987494252265</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01434303352243776</v>
+        <v>0.002466695254996821</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>11.09773831266038</v>
+        <v>1.912093724905556</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.007334573644222652</v>
+        <v>0.001259367644650069</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>11.09805589119665</v>
+        <v>1.912144317334213</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002753845523131985</v>
+        <v>0.0004703237279909154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>11.09622420543614</v>
+        <v>1.911824389174857</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001498985896542432</v>
+        <v>0.0002540518768592011</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>11.09646603752376</v>
+        <v>1.911861972613917</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0007189989849586371</v>
+        <v>0.0001197726022376576</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>11.0964048938073</v>
+        <v>1.911847271824636</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004436835335503784</v>
+        <v>7.273245427736819e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>11.09657212823842</v>
+        <v>1.911872110684413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000229696167906683</v>
+        <v>3.514539714193261e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>11.09658757635195</v>
+        <v>1.911870653856644</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0001088966169095103</v>
+        <v>1.498186261570356e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>11.09657552648654</v>
+        <v>1.911864417038152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.791134353247457e-05</v>
+        <v>7.791463777627117e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>11.09660240241643</v>
+        <v>1.911865009306555</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.763711577382715e-05</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>11.09659088348747</v>
+        <v>1.911858865510579</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>9.411168204796322e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>11.09658191018411</v>
+        <v>1.911853180976551</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>11.09657815110299</v>
+        <v>1.911848429701337</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-1.124731583660385e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>11.09657199451274</v>
+        <v>1.911843140553775</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>11.0965669012706</v>
+        <v>1.911843117819474</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>11.09656253629664</v>
+        <v>1.91184343609969</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.828705708809411</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>11.09656362754309</v>
+        <v>1.911844527346148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>11.09656293793596</v>
+        <v>1.911843837739012</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>11.09656296824836</v>
+        <v>1.911843868051413</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>11.09656277879585</v>
+        <v>1.911843678598903</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>11.09656283184255</v>
+        <v>1.911843731645606</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>11.09656288488925</v>
+        <v>1.911843784692309</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>11.09656284699875</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>11.09656271817104</v>
+        <v>1.9118436179741</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>11.09656257418714</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>11.09656246809373</v>
+        <v>1.911843367896787</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>11.09656223317262</v>
+        <v>1.911843132975675</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>11.09656239989083</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>11.09656259692144</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>11.09656243778133</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>11.09656247567183</v>
+        <v>1.911843375474887</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>11.09656267270244</v>
+        <v>1.911843572505498</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>11.09656264996814</v>
+        <v>1.911843549771197</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>11.09656249840613</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>11.09656242262513</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>11.09656252114043</v>
+        <v>1.91184342094349</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>11.09656252871853</v>
+        <v>1.91184342852159</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>11.09656279395205</v>
+        <v>1.911843693755104</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>11.09656249840613</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>11.09656274090535</v>
+        <v>1.911843640708401</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>11.09656282426445</v>
+        <v>1.911843724067505</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>11.09656265754624</v>
+        <v>1.911843557349297</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>11.09656284699875</v>
+        <v>1.911843746801807</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>11.09656249840613</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>11.09656229379742</v>
+        <v>1.911843193600478</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>11.09656240746893</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>11.09656242262513</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>11.09656218770402</v>
+        <v>1.911843087507072</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>11.09656224832882</v>
+        <v>1.911843148131875</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>11.09656211950111</v>
+        <v>1.911843019304169</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>11.09656225590692</v>
+        <v>1.911843155709976</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>11.09656243020323</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>11.09656257418714</v>
+        <v>1.911843473990193</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>11.09656240746893</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>11.09656239989083</v>
+        <v>1.911843299693883</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>11.09656211192301</v>
+        <v>1.911843011726068</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>11.09656212707921</v>
+        <v>1.911843026882269</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>11.09656235442223</v>
+        <v>1.911843254225281</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>11.09656233926602</v>
+        <v>1.91184323906908</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>11.09656244535943</v>
+        <v>1.911843345162486</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>11.09656217254781</v>
+        <v>1.911843072350872</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>11.09656227106312</v>
+        <v>1.911843170866177</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>11.09656242262513</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>11.09656243778133</v>
+        <v>1.911843337584386</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>11.09656249840613</v>
+        <v>1.911843398209189</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>11.09656259692144</v>
+        <v>1.911843496724494</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>11.09656243020323</v>
+        <v>1.911843330006285</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>11.09656238473463</v>
+        <v>1.911843284537683</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>11.09656236957843</v>
+        <v>1.911843269381482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>11.09656240746893</v>
+        <v>1.911843307271984</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>11.09656242262513</v>
+        <v>1.911843322428185</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>11.09656241504703</v>
+        <v>1.911843314850084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>3.228705708809411</v>
+        <v>1.446163885826609</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>3.228705708809411</v>
+        <v>2.379683914612168</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>3.228705708809411</v>
+        <v>1.446163885826609</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.828705708809411</v>
+        <v>2.579683914612168</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000391969883532729</v>
+        <v>-0.0002967218343935674</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>4.518833854729427</v>
+        <v>3.420764520504178</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.828705708809411</v>
+        <v>1.646163885826609</v>
       </c>
       <c r="JC40" t="n">
-        <v>9.044653011089986</v>
+        <v>6.846816925615971</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.6776192940205544</v>
+        <v>0.5129588764222104</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC41" t="n">
-        <v>5.874992847803057</v>
+        <v>4.447379066868219</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.8472445438445323</v>
+        <v>0.6413655015522323</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC42" t="n">
-        <v>6.891970365717502</v>
+        <v>5.217232723200267</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>1.214521198302129</v>
+        <v>0.9193944048623071</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC43" t="n">
-        <v>8.474246242655786</v>
+        <v>6.415018194499348</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.299297110085373</v>
+        <v>0.9835698997565723</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.5126438570410506</v>
       </c>
       <c r="JC44" t="n">
-        <v>9.85840981704181</v>
+        <v>7.462832508871292</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.376992313482098</v>
+        <v>1.042385846046838</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.228705708809411</v>
+        <v>1.446163885826609</v>
       </c>
       <c r="JC45" t="n">
-        <v>11.31319712833096</v>
+        <v>8.564109508476889</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.6214110207047058</v>
+        <v>0.4704093452214653</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>3.828705708809411</v>
+        <v>1.446163885826609</v>
       </c>
       <c r="JC46" t="n">
-        <v>11.17788243713265</v>
+        <v>8.461675990392404</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.3001137636143597</v>
+        <v>0.2271868561202745</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC47" t="n">
-        <v>11.15621033973502</v>
+        <v>8.445270159436824</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.142994660511181</v>
+        <v>0.1082471602624951</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC48" t="n">
-        <v>11.14184879192911</v>
+        <v>8.434398432702642</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.04236868364818479</v>
+        <v>0.03207287851121161</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC49" t="n">
-        <v>11.08343795528665</v>
+        <v>8.39018122563005</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02802530428311959</v>
+        <v>0.02121501312091727</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC50" t="n">
-        <v>11.09709775777395</v>
+        <v>8.400521861713974</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01434303352243776</v>
+        <v>0.01085688054136541</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC51" t="n">
-        <v>11.09773831266038</v>
+        <v>8.401005565622306</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.007334573644222652</v>
+        <v>0.005550768336643097</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC52" t="n">
-        <v>11.09805589119665</v>
+        <v>8.401244767610708</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002753845523131985</v>
+        <v>0.002084002371425042</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC53" t="n">
-        <v>11.09622420543614</v>
+        <v>8.399856787504911</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001498985896542432</v>
+        <v>0.001133508248616871</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC54" t="n">
-        <v>11.09646603752376</v>
+        <v>8.400038637905856</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0007189989849586371</v>
+        <v>0.0005433636658852466</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC55" t="n">
-        <v>11.0964048938073</v>
+        <v>8.399991137083902</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0004436835335503784</v>
+        <v>0.0003344645155150889</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC56" t="n">
-        <v>11.09657212823842</v>
+        <v>8.400116446028498</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.000229696167906683</v>
+        <v>0.0001720514950874977</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC57" t="n">
-        <v>11.09658757635195</v>
+        <v>8.400126917266954</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0001088966169095103</v>
+        <v>8.092200924752528e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC58" t="n">
-        <v>11.09657552648654</v>
+        <v>8.400116568635035</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.791134353247457e-05</v>
+        <v>5.00032942437966e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC59" t="n">
-        <v>11.09660240241643</v>
+        <v>8.400135895778877</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.763711577382715e-05</v>
+        <v>2.064344810800705e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC60" t="n">
-        <v>11.09659088348747</v>
+        <v>8.400125863076584</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>9.411168204796322e-06</v>
+        <v>6.323060732339969e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC61" t="n">
-        <v>11.09658191018411</v>
+        <v>8.400117848371369</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>2.788397616378431e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC62" t="n">
-        <v>11.09657815110299</v>
+        <v>8.400113758558881</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-1.124731583660385e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC63" t="n">
-        <v>11.09657199451274</v>
+        <v>8.400107891116196</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-3.107779831880603e-06</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC64" t="n">
-        <v>11.0965669012706</v>
+        <v>8.400102821760827</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8554444171274074</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC65" t="n">
-        <v>11.09656253629664</v>
+        <v>8.400098456786861</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.828705708809411</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC66" t="n">
-        <v>11.09656362754309</v>
+        <v>8.400099548033316</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2554444171274073</v>
+        <v>0.7126438570410507</v>
       </c>
       <c r="JC67" t="n">
-        <v>11.09656293793596</v>
+        <v>8.40009885842618</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2554444171274073</v>
+        <v>-0.2208761717445079</v>
       </c>
       <c r="JC68" t="n">
-        <v>11.09656296824836</v>
+        <v>8.400098888738581</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.2208761717445079</v>
       </c>
       <c r="JC69" t="n">
-        <v>11.09656277879585</v>
+        <v>8.400098699286072</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC70" t="n">
-        <v>11.09656283184255</v>
+        <v>8.400098752332775</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC71" t="n">
-        <v>11.09656288488925</v>
+        <v>8.400098805379477</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC72" t="n">
-        <v>11.09656284699875</v>
+        <v>8.400098767488975</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC73" t="n">
-        <v>11.09656271817104</v>
+        <v>8.400098638661269</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC74" t="n">
-        <v>11.09656257418714</v>
+        <v>8.40009849467736</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC75" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC76" t="n">
-        <v>11.09656246809373</v>
+        <v>8.400098388583956</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC77" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC78" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC79" t="n">
-        <v>11.09656223317262</v>
+        <v>8.400098153662844</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC80" t="n">
-        <v>11.09656239989083</v>
+        <v>8.400098320381053</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC81" t="n">
-        <v>11.09656259692144</v>
+        <v>8.400098517411662</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC82" t="n">
-        <v>11.09656243778133</v>
+        <v>8.400098358271554</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC83" t="n">
-        <v>11.09656247567183</v>
+        <v>8.400098396162056</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC84" t="n">
-        <v>11.09656267270244</v>
+        <v>8.400098593192666</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC85" t="n">
-        <v>11.09656264996814</v>
+        <v>8.400098570458365</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC86" t="n">
-        <v>11.09656249840613</v>
+        <v>8.400098418896357</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC87" t="n">
-        <v>11.09656242262513</v>
+        <v>8.400098343115355</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC88" t="n">
-        <v>11.09656252114043</v>
+        <v>8.400098441630657</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC89" t="n">
-        <v>11.09656252871853</v>
+        <v>8.400098449208759</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC90" t="n">
-        <v>11.09656279395205</v>
+        <v>8.400098714442272</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC91" t="n">
-        <v>11.09656249840613</v>
+        <v>8.400098418896357</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC92" t="n">
-        <v>11.09656274090535</v>
+        <v>8.400098661395571</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC93" t="n">
-        <v>11.09656282426445</v>
+        <v>8.400098744754674</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC94" t="n">
-        <v>11.09656265754624</v>
+        <v>8.400098578036465</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC95" t="n">
-        <v>11.09656284699875</v>
+        <v>8.400098767488975</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC96" t="n">
-        <v>11.09656249840613</v>
+        <v>8.400098418896357</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC97" t="n">
-        <v>11.09656229379742</v>
+        <v>8.400098214287645</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC98" t="n">
-        <v>11.09656240746893</v>
+        <v>8.400098327959151</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC99" t="n">
-        <v>11.09656242262513</v>
+        <v>8.400098343115355</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC100" t="n">
-        <v>11.09656218770402</v>
+        <v>8.400098108194241</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC101" t="n">
-        <v>11.09656224832882</v>
+        <v>8.400098168819044</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC102" t="n">
-        <v>11.09656211950111</v>
+        <v>8.400098039991338</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC103" t="n">
-        <v>11.09656225590692</v>
+        <v>8.400098176397146</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC104" t="n">
-        <v>11.09656243020323</v>
+        <v>8.400098350693453</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC105" t="n">
-        <v>11.09656257418714</v>
+        <v>8.40009849467736</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC106" t="n">
-        <v>11.09656240746893</v>
+        <v>8.400098327959151</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC107" t="n">
-        <v>11.09656239989083</v>
+        <v>8.400098320381053</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC108" t="n">
-        <v>11.09656211192301</v>
+        <v>8.400098032413236</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC109" t="n">
-        <v>11.09656212707921</v>
+        <v>8.400098047569436</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC110" t="n">
-        <v>11.09656235442223</v>
+        <v>8.40009827491245</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC111" t="n">
-        <v>11.09656233926602</v>
+        <v>8.400098259756248</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC112" t="n">
-        <v>11.09656244535943</v>
+        <v>8.400098365849654</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC113" t="n">
-        <v>11.09656217254781</v>
+        <v>8.400098093038039</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC114" t="n">
-        <v>11.09656227106312</v>
+        <v>8.400098191553345</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC115" t="n">
-        <v>11.09656242262513</v>
+        <v>8.400098343115355</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC116" t="n">
-        <v>11.09656243778133</v>
+        <v>8.400098358271554</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC117" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC118" t="n">
-        <v>11.09656249840613</v>
+        <v>8.400098418896357</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC119" t="n">
-        <v>11.09656259692144</v>
+        <v>8.400098517411662</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC120" t="n">
-        <v>11.09656243020323</v>
+        <v>8.400098350693453</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC121" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC122" t="n">
-        <v>11.09656238473463</v>
+        <v>8.400098305224851</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC123" t="n">
-        <v>11.09656236957843</v>
+        <v>8.40009829006865</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC124" t="n">
-        <v>11.09656240746893</v>
+        <v>8.400098327959151</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC125" t="n">
-        <v>11.09656242262513</v>
+        <v>8.400098343115355</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8554444171274074</v>
+        <v>-0.420876171744508</v>
       </c>
       <c r="JC126" t="n">
-        <v>11.09656241504703</v>
+        <v>8.400098335537253</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02250736765563488</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.420876171744508</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01286826841533184</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007448658347129822</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.003906309604644775</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.002427499741315842</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001838576048612595</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001598764210939407</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001362990587949753</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.00109405443072319</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.000855516642332077</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0007177144289016724</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0006232894957065582</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0003990717232227325</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0002738088369369507</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0001444369554519653</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0001912973821163177</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0001656711101531982</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001545436680316925</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-2.181529998779297e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0001651234924793243</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.646163885826609</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.000486765056848526</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.579683914612168</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0009965188801288605</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.579683914612168</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0009033344686031342</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.579683914612168</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0005540773272514343</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.579683914612168</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0002180151641368866</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.646163885826609</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-1.773238182067871e-05</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7126438570410507</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0001892298460006714</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5126438570410506</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>6.027519702911377e-06</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.446163885826609</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.000170782208442688</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.379683914612168</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0001033283770084381</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.646163885826609</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-5.420297384262085e-06</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5126438570410506</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0001548118889331818</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0001844353973865509</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.000135030597448349</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5126438570410506</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.000300724059343338</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.446163885826609</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001719210296869278</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.579683914612168</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001561153680086136</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.579683914612168</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0009205378592014313</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.579683914612168</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002967218343935674</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.420764520504178</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0001213885843753815</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.646163885826609</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.846816925615971</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5129588764222104</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.000614408403635025</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7126438570410507</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.447379066868219</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6413655015522323</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001264601945877075</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.217232723200267</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9193944048623071</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0009331554174423218</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.415018194499348</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9835698997565723</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0003088749945163727</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5126438570410506</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.462832508871292</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.042385846046838</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.000265173614025116</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.446163885826609</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.564109508476889</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4704093452214653</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0002356357872486115</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.446163885826609</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.461675990392404</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2271868561202745</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.00208636000752449</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7126438570410507</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.445270159436824</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1082471602624951</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.003464337438344955</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.434398432702642</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.03207287851121161</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.005010858178138733</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.39018122563005</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02121501312091727</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.005438867956399918</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.400521861713974</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01085688054136541</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.005777508020401001</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.401005565622306</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005550768336643097</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.005444634705781937</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.401244767610708</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002084002371425042</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005061376839876175</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.399856787504911</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001133508248616871</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.004732672125101089</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.400038637905856</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005433636658852466</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.004371851682662964</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.399991137083902</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003344645155150889</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003881648182868958</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.400116446028498</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001720514950874977</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003970380872488022</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.400126917266954</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.092200924752528e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.00192449614405632</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.400116568635035</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.00032942437966e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001928430050611496</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.400135895778877</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003412380814552307</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.400125863076584</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00446087121963501</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.400117848371369</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004867579787969589</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.400113758558881</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.004929199814796448</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.400107891116196</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004290714859962463</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.400102821760827</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002504948526620865</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.400098456786861</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0002561062574386597</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.400099548033316</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.001113105565309525</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7126438570410507</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.40009885842618</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003986340016126633</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2208761717445079</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.400098888738581</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006176967173814774</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2208761717445079</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.400098699286072</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007291283458471298</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.400098752332775</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007902290672063828</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.400098805379477</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007854131981730461</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.400098767488975</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.007329579442739487</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.400098638661269</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.006721340119838715</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.40009849467736</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00615360215306282</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.005561117082834244</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.400098388583956</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.005296729505062103</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004888709634542465</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00423552468419075</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.400098153662844</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003617975860834122</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.400098320381053</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003732036799192429</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.400098517411662</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004035066813230515</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.400098358271554</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003729313611984253</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.400098396162056</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003327455371618271</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.400098593192666</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003637582063674927</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.400098570458365</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.004153043031692505</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.400098418896357</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.004344500601291656</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.400098343115355</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.00423184409737587</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.400098441630657</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.003712419420480728</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.400098449208759</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003607232123613358</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.400098714442272</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.00388525053858757</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.400098418896357</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003711532801389694</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.400098661395571</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.004071325063705444</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.400098744754674</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.00339077040553093</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.400098578036465</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003822498023509979</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.400098767488975</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00468079000711441</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.400098418896357</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005422104150056839</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.400098214287645</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005518294870853424</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.400098327959151</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005165211856365204</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.400098343115355</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.004793055355548859</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.400098108194241</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004591628909111023</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.400098168819044</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004306130111217499</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.400098039991338</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003198746591806412</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.400098176397146</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0030243881046772</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.400098350693453</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003242697566747665</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.40009849467736</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003340695053339005</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.400098327959151</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003591384738683701</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.400098320381053</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003950931131839752</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.400098032413236</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003854874521493912</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.400098047569436</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003616049885749817</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.40009827491245</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003146577626466751</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.400098259756248</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003238633275032043</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.400098365849654</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003376558423042297</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.400098093038039</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003192629665136337</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.400098191553345</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002998892217874527</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.400098343115355</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002930901944637299</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.400098358271554</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00288647785782814</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002790957689285278</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.400098418896357</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003034569323062897</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.400098517411662</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003356590867042542</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.400098350693453</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003448974341154099</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003426820039749146</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.400098305224851</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003327291458845139</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.40009829006865</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003318347036838531</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.420876171744508</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.400098327959151</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003191441297531128</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.420876171744508</v>
+        <v>0.1900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.400098343115355</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003007490187883377</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.420876171744508</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.400098335537253</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000007.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02250736765563488</v>
+        <v>-0.02250736951828003</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.01286826841533184</v>
+        <v>-0.01286837086081505</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.007448658347129822</v>
+        <v>-0.007448706775903702</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.003906309604644775</v>
+        <v>-0.003906358033418655</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.002427499741315842</v>
+        <v>-0.002427477389574051</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001838576048612595</v>
+        <v>-0.001838579773902893</v>
       </c>
       <c r="JB7" t="n">
         <v>0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.00109405443072319</v>
+        <v>-0.001094058156013489</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.000855516642332077</v>
+        <v>-0.000855524092912674</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0007177144289016724</v>
+        <v>-0.0007178224623203278</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0006232894957065582</v>
+        <v>-0.0006235353648662567</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0003990717232227325</v>
+        <v>-0.0003992021083831787</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0002738088369369507</v>
+        <v>-0.0002738721668720245</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0001444369554519653</v>
+        <v>-0.000144563615322113</v>
       </c>
       <c r="JB16" t="n">
         <v>0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.0001912973821163177</v>
+        <v>-0.0001913830637931824</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0001656711101531982</v>
+        <v>-0.0001657195389270782</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0001545436680316925</v>
+        <v>-0.0001545324921607971</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-2.181529998779297e-05</v>
+        <v>-2.180784940719604e-05</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0001651234924793243</v>
+        <v>0.0001650303602218628</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.000486765056848526</v>
+        <v>0.0004867240786552429</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0009965188801288605</v>
+        <v>0.0009964928030967712</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3999999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0009033344686031342</v>
+        <v>0.0009033046662807465</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3999999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.0005540773272514343</v>
+        <v>0.000554010272026062</v>
       </c>
       <c r="JB25" t="n">
         <v>0.2599999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0002180151641368866</v>
+        <v>0.0002179406583309174</v>
       </c>
       <c r="JB26" t="n">
         <v>0.1199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-1.773238182067871e-05</v>
+        <v>-1.778826117515564e-05</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.02000000000000007</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0001892298460006714</v>
+        <v>-0.0001893229782581329</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.16</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>6.027519702911377e-06</v>
+        <v>5.982816219329834e-06</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.000170782208442688</v>
+        <v>0.0001707188785076141</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.0001033283770084381</v>
+        <v>0.0001032911241054535</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-5.420297384262085e-06</v>
+        <v>-5.45009970664978e-06</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.02000000000000007</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0001548118889331818</v>
+        <v>-0.0001548156142234802</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.02000000000000007</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0001844353973865509</v>
+        <v>-0.0001844391226768494</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.000135030597448349</v>
+        <v>-0.0001350380480289459</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.000300724059343338</v>
+        <v>0.000300675630569458</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001719210296869278</v>
+        <v>0.001719255000352859</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001561153680086136</v>
+        <v>0.001561161130666733</v>
       </c>
       <c r="JB38" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0001213885843753815</v>
+        <v>0.000121384859085083</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.000614408403635025</v>
+        <v>-0.0006144270300865173</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.5799999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001264601945877075</v>
+        <v>-0.001264598220586777</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0009331554174423218</v>
+        <v>-0.0009331516921520233</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0003088749945163727</v>
+        <v>-0.0003089196979999542</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.000265173614025116</v>
+        <v>0.0002651698887348175</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0002356357872486115</v>
+        <v>0.0002354420721530914</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.00208636000752449</v>
+        <v>-0.002086564898490906</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.003464337438344955</v>
+        <v>-0.003464478999376297</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.005010858178138733</v>
+        <v>-0.00501096248626709</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.005438867956399918</v>
+        <v>-0.005438864231109619</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.005777508020401001</v>
+        <v>-0.005777444690465927</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.005444634705781937</v>
+        <v>-0.00544457882642746</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.005061376839876175</v>
+        <v>-0.005061309784650803</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.004732672125101089</v>
+        <v>-0.004732582718133926</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.004371851682662964</v>
+        <v>-0.004371825605630875</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003881648182868958</v>
+        <v>-0.003881692886352539</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003970380872488022</v>
+        <v>-0.003970388323068619</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.00192449614405632</v>
+        <v>-0.001924484968185425</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.001928430050611496</v>
+        <v>-0.001928124576807022</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003412380814552307</v>
+        <v>-0.003412246704101562</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.00446087121963501</v>
+        <v>-0.004460830241441727</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.004867579787969589</v>
+        <v>-0.004867549985647202</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.004929199814796448</v>
+        <v>-0.004929147660732269</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.2599999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002504948526620865</v>
+        <v>-0.002504833042621613</v>
       </c>
       <c r="JB65" t="n">
         <v>0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.0002561062574386597</v>
+        <v>0.0002559199929237366</v>
       </c>
       <c r="JB66" t="n">
         <v>0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.001113105565309525</v>
+        <v>-0.001113604754209518</v>
       </c>
       <c r="JB67" t="n">
         <v>0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003986340016126633</v>
+        <v>-0.0039866603910923</v>
       </c>
       <c r="JB68" t="n">
         <v>0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.006176967173814774</v>
+        <v>-0.006177261471748352</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.007291283458471298</v>
+        <v>-0.007291354238986969</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.007902290672063828</v>
+        <v>-0.007902132347226143</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.007854131981730461</v>
+        <v>-0.007854003459215164</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.007329579442739487</v>
+        <v>-0.007329490035772324</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.006721340119838715</v>
+        <v>-0.006721246987581253</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.00615360215306282</v>
+        <v>-0.006153572350740433</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.005561117082834244</v>
+        <v>-0.005561109632253647</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.005296729505062103</v>
+        <v>-0.005296703428030014</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.004888709634542465</v>
+        <v>-0.004888661205768585</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.00423552468419075</v>
+        <v>-0.004235528409481049</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003617975860834122</v>
+        <v>-0.003617927432060242</v>
       </c>
       <c r="JB80" t="n">
         <v>0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.003732036799192429</v>
+        <v>-0.003732006996870041</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.004035066813230515</v>
+        <v>-0.004035085439682007</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.003729313611984253</v>
+        <v>-0.003729365766048431</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.003327455371618271</v>
+        <v>-0.003327459096908569</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.003637582063674927</v>
+        <v>-0.003637615591287613</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.004153043031692505</v>
+        <v>-0.004153039306402206</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.004344500601291656</v>
+        <v>-0.004344504326581955</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.00423184409737587</v>
+        <v>-0.004231836646795273</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.16</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.003712419420480728</v>
+        <v>-0.003712553530931473</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.02000000000000007</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003607232123613358</v>
+        <v>-0.003607291728258133</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.00388525053858757</v>
+        <v>-0.003885246813297272</v>
       </c>
       <c r="JB91" t="n">
         <v>0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003711532801389694</v>
+        <v>-0.003711525350809097</v>
       </c>
       <c r="JB92" t="n">
         <v>0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.004071325063705444</v>
+        <v>-0.004071280360221863</v>
       </c>
       <c r="JB93" t="n">
         <v>0.8599999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.00339077040553093</v>
+        <v>-0.003390789031982422</v>
       </c>
       <c r="JB94" t="n">
         <v>0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003822498023509979</v>
+        <v>-0.003822490572929382</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00468079000711441</v>
+        <v>-0.00468069314956665</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.005422104150056839</v>
+        <v>-0.00542202964425087</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005518294870853424</v>
+        <v>-0.00551823154091835</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.005165211856365204</v>
+        <v>-0.005165260285139084</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.004793055355548859</v>
+        <v>-0.004793133586645126</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.004306130111217499</v>
+        <v>-0.004306141287088394</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003198746591806412</v>
+        <v>-0.003198768943548203</v>
       </c>
       <c r="JB103" t="n">
         <v>0.8599999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.0030243881046772</v>
+        <v>-0.003024362027645111</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003242697566747665</v>
+        <v>-0.003242678940296173</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003340695053339005</v>
+        <v>-0.003340642899274826</v>
       </c>
       <c r="JB106" t="n">
         <v>0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003591384738683701</v>
+        <v>-0.003591321408748627</v>
       </c>
       <c r="JB107" t="n">
         <v>0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003950931131839752</v>
+        <v>-0.003950834274291992</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003854874521493912</v>
+        <v>-0.00385473296046257</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003616049885749817</v>
+        <v>-0.003615982830524445</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.02000000000000007</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003146577626466751</v>
+        <v>-0.00314658135175705</v>
       </c>
       <c r="JB111" t="n">
         <v>0.1199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003238633275032043</v>
+        <v>-0.003238655626773834</v>
       </c>
       <c r="JB112" t="n">
         <v>0.2599999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003376558423042297</v>
+        <v>-0.003376562148332596</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003192629665136337</v>
+        <v>-0.003192644566297531</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002998892217874527</v>
+        <v>-0.002998925745487213</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002930901944637299</v>
+        <v>-0.002930823713541031</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00288647785782814</v>
+        <v>-0.002886462956666946</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002790957689285278</v>
+        <v>-0.002790983766317368</v>
       </c>
       <c r="JB118" t="n">
         <v>0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003034569323062897</v>
+        <v>-0.003034360706806183</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003356590867042542</v>
+        <v>-0.003356471657752991</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003448974341154099</v>
+        <v>-0.00344877690076828</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003426820039749146</v>
+        <v>-0.003426790237426758</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003327291458845139</v>
+        <v>-0.003327231854200363</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003318347036838531</v>
+        <v>-0.003318261355161667</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.003191441297531128</v>
+        <v>-0.003191448748111725</v>
       </c>
       <c r="JB125" t="n">
         <v>0.1900000000000003</v>
